--- a/reports/pdf_change_20260803.xlsx
+++ b/reports/pdf_change_20260803.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -962,121 +962,385 @@
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="F18" s="19" t="n"/>
-      <c r="G18" s="19" t="n"/>
-      <c r="H18" s="19" t="n"/>
-      <c r="I18" s="19" t="n"/>
-      <c r="J18" s="19" t="n"/>
-      <c r="K18" s="19" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="19" t="n"/>
-      <c r="F20" s="19" t="n"/>
-      <c r="G20" s="19" t="n"/>
-      <c r="H20" s="19" t="n"/>
-      <c r="I20" s="19" t="n"/>
-      <c r="J20" s="19" t="n"/>
-      <c r="K20" s="19" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,812억   ·   현금 40억(1.9%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 0종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>-597849000</v>
+      </c>
+      <c r="J21" s="17" t="inlineStr">
+        <is>
+          <t>4.92%→4.98%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>130→123</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,799억   ·   현금 18억(0.9%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 2종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>7630429000</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>8.98%→12.24%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>249→371</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>-90</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>-2858220000</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>7.12%→5.51%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>419→329</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>581828000</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>6.67%→7.13%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>578→604</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I27" s="16" t="n">
+        <v>-3798565000</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>7.03%→5.01%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>119→85</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 212억   ·   현금 7억(3.4%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 418억   ·   현금 13억(2.8%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="19" t="n"/>
-      <c r="F28" s="19" t="n"/>
-      <c r="G28" s="19" t="n"/>
-      <c r="H28" s="19" t="n"/>
-      <c r="I28" s="19" t="n"/>
-      <c r="J28" s="19" t="n"/>
-      <c r="K28" s="19" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="20" t="n"/>
+      <c r="J35" s="20" t="n"/>
+      <c r="K35" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A4:E4"/>
+  <mergeCells count="19">
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="G19:K19"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="G24:K24"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G13:K13"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A32:K32"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260803.xlsx
+++ b/reports/pdf_change_20260803.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,286억   ·   현금 127억(3.3%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 5종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,907억   ·   현금 129억(3.3%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 5종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>46</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>404168880</v>
+        <v>408198480</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>770905800</v>
+        <v>778591800</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>397188000</v>
+        <v>401148000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>385452900</v>
+        <v>389295900</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>369304600</v>
+        <v>372986600</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,004억   ·   현금 13억(0.4%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,202억   ·   현금 13억(0.4%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -964,7 +964,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,812억   ·   현금 40억(1.9%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 0종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,154억   ·   현금 40억(1.9%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1065,7 +1065,7 @@
         <v>-7</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>-597849000</v>
+        <v>-596977500</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,799억   ·   현금 18억(0.9%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 2종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,919억   ·   현금 18억(0.9%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1258,7 +1258,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 212억   ·   현금 7억(3.4%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 241억   ·   현금 7억(2.9%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1282,7 +1282,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 418억   ·   현금 13억(2.8%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 446억   ·   현금 13억(2.8%)      당일 2026-08-03  vs  전영업일 2026-07-31      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
